--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:26</t>
+    <t xml:space="preserve">2026-08-02 20:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 20:02</t>
+    <t xml:space="preserve">2026-08-05 10:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:59</t>
+    <t xml:space="preserve">2026-08-16 10:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:06</t>
+    <t xml:space="preserve">2026-08-19 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:59</t>
+    <t xml:space="preserve">2026-08-28 12:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2023_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:20</t>
+    <t xml:space="preserve">2026-09-06 17:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
